--- a/zawodnicy_tr.xlsx
+++ b/zawodnicy_tr.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[Arabia Saudyjska] Al-Ahli SFC</t>
+          <t>[Arabia Saudyjska] Al Ahli</t>
         </is>
       </c>
     </row>
